--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:45</t>
+    <t xml:space="preserve">2026-09-09 22:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:33</t>
+    <t xml:space="preserve">2026-09-12 19:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:49</t>
+    <t xml:space="preserve">2026-09-24 00:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:27</t>
+    <t xml:space="preserve">2026-09-27 23:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -580,7 +580,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8.77</v>
+        <v>87.72</v>
       </c>
     </row>
     <row r="3">
@@ -597,7 +597,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7.46</v>
+        <v>74.6</v>
       </c>
     </row>
     <row r="4">
@@ -614,7 +614,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5.09</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="5">
@@ -631,7 +631,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3.92</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="6">
@@ -648,7 +648,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3.5</v>
+        <v>34.95</v>
       </c>
     </row>
     <row r="7">
@@ -665,7 +665,7 @@
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2.35</v>
+        <v>23.55</v>
       </c>
     </row>
     <row r="8">
@@ -682,7 +682,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>2.16</v>
+        <v>21.65</v>
       </c>
     </row>
     <row r="9">
@@ -699,7 +699,7 @@
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2</v>
+        <v>19.96</v>
       </c>
     </row>
     <row r="10">
@@ -716,7 +716,7 @@
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.59</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="11">
@@ -733,7 +733,7 @@
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1.44</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="12">
@@ -750,7 +750,7 @@
         <v>2020</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1.42</v>
+        <v>14.23</v>
       </c>
     </row>
     <row r="13">
@@ -767,7 +767,7 @@
         <v>2020</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1.33</v>
+        <v>13.26</v>
       </c>
     </row>
     <row r="14">
@@ -784,7 +784,7 @@
         <v>2020</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1.27</v>
+        <v>12.69</v>
       </c>
     </row>
     <row r="15">
@@ -801,7 +801,7 @@
         <v>2020</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1.26</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="16">
@@ -818,7 +818,7 @@
         <v>2020</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.12</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="17">
@@ -835,7 +835,7 @@
         <v>2020</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.04</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="18">
@@ -852,7 +852,7 @@
         <v>2020</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.59</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="19">
@@ -869,7 +869,7 @@
         <v>2020</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.55</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="20">
@@ -886,7 +886,7 @@
         <v>2020</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.49</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="21">
@@ -903,7 +903,7 @@
         <v>2020</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.4</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="22">
@@ -920,7 +920,7 @@
         <v>2020</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.31</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="23">
@@ -937,7 +937,7 @@
         <v>2020</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.31</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="24">
@@ -954,7 +954,7 @@
         <v>2020</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.21</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="25">
@@ -971,7 +971,7 @@
         <v>2020</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.2</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="26">
@@ -1005,7 +1005,7 @@
         <v>2020</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="28">
@@ -1022,7 +1022,7 @@
         <v>2020</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="29">
@@ -1039,7 +1039,7 @@
         <v>2020</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>-0.13</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="30">
@@ -1056,7 +1056,7 @@
         <v>2020</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-0.15</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="31">
@@ -1073,7 +1073,7 @@
         <v>2020</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-0.53</v>
+        <v>-5.26</v>
       </c>
     </row>
     <row r="32">
@@ -1090,7 +1090,7 @@
         <v>2020</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-0.55</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="33">
@@ -1107,7 +1107,7 @@
         <v>2020</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-0.7</v>
+        <v>-6.99</v>
       </c>
     </row>
     <row r="34">
@@ -1124,7 +1124,7 @@
         <v>2020</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-1.28</v>
+        <v>-12.81</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:10</t>
+    <t xml:space="preserve">2026-10-01 20:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:56</t>
+    <t xml:space="preserve">2026-10-02 13:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:26</t>
+    <t xml:space="preserve">2026-10-04 08:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2020_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:13</t>
+    <t xml:space="preserve">2026-10-05 08:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
